--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/65.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/65.xlsx
@@ -426,13 +426,13 @@
         <v>-2.644061201730449</v>
       </c>
       <c r="E2">
-        <v>-29.39824851898653</v>
+        <v>-37.92885200041572</v>
       </c>
       <c r="F2">
-        <v>-7.30303875525018</v>
+        <v>-8.432587304951451</v>
       </c>
       <c r="G2">
-        <v>-19.49999498208907</v>
+        <v>-21.88503447876499</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.353722755397513</v>
       </c>
       <c r="E3">
-        <v>-31.57008653916921</v>
+        <v>-38.87017457120514</v>
       </c>
       <c r="F3">
-        <v>-6.93709420492846</v>
+        <v>-8.811272373436402</v>
       </c>
       <c r="G3">
-        <v>-19.2835366172766</v>
+        <v>-21.96639444593812</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.176449544012002</v>
       </c>
       <c r="E4">
-        <v>-32.55273369951562</v>
+        <v>-36.78486889659804</v>
       </c>
       <c r="F4">
-        <v>-6.795684311885914</v>
+        <v>-8.571605406135205</v>
       </c>
       <c r="G4">
-        <v>-18.28906363473446</v>
+        <v>-22.7228805860259</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.131873813790596</v>
       </c>
       <c r="E5">
-        <v>-32.30044335560029</v>
+        <v>-38.40075974828105</v>
       </c>
       <c r="F5">
-        <v>-6.768317081814162</v>
+        <v>-8.471123225065361</v>
       </c>
       <c r="G5">
-        <v>-19.04141490344369</v>
+        <v>-22.48362911517554</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.19036784819252</v>
       </c>
       <c r="E6">
-        <v>-33.50740621167965</v>
+        <v>-38.40499387147822</v>
       </c>
       <c r="F6">
-        <v>-6.927967703664261</v>
+        <v>-9.071814960261966</v>
       </c>
       <c r="G6">
-        <v>-19.32299997537748</v>
+        <v>-22.86988867124277</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.326077222402623</v>
       </c>
       <c r="E7">
-        <v>-32.95693396825526</v>
+        <v>-39.12131921119654</v>
       </c>
       <c r="F7">
-        <v>-6.806033434116832</v>
+        <v>-8.152961457771321</v>
       </c>
       <c r="G7">
-        <v>-18.0372685068358</v>
+        <v>-22.10958216160267</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.504572359499839</v>
       </c>
       <c r="E8">
-        <v>-33.14497432294976</v>
+        <v>-40.00468184316178</v>
       </c>
       <c r="F8">
-        <v>-6.81595851908889</v>
+        <v>-8.539190113457989</v>
       </c>
       <c r="G8">
-        <v>-18.58296062552879</v>
+        <v>-22.39948166865834</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.692079598802545</v>
       </c>
       <c r="E9">
-        <v>-32.96531617364346</v>
+        <v>-40.61917312363261</v>
       </c>
       <c r="F9">
-        <v>-6.526410358422054</v>
+        <v>-8.687378267818616</v>
       </c>
       <c r="G9">
-        <v>-18.14919143042748</v>
+        <v>-21.91040649977796</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.85518679057165</v>
       </c>
       <c r="E10">
-        <v>-33.4267880531581</v>
+        <v>-40.56673339462378</v>
       </c>
       <c r="F10">
-        <v>-6.73408488252546</v>
+        <v>-8.226284666097294</v>
       </c>
       <c r="G10">
-        <v>-18.18324204657165</v>
+        <v>-22.61449829088847</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.969795309726011</v>
       </c>
       <c r="E11">
-        <v>-33.79764516777926</v>
+        <v>-40.12975376677962</v>
       </c>
       <c r="F11">
-        <v>-6.530551749390928</v>
+        <v>-8.088954795419399</v>
       </c>
       <c r="G11">
-        <v>-18.67405194131461</v>
+        <v>-21.81589207990454</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.018239692835818</v>
       </c>
       <c r="E12">
-        <v>-34.36199491980016</v>
+        <v>-40.73862068253293</v>
       </c>
       <c r="F12">
-        <v>-6.565456231840735</v>
+        <v>-7.72751747213302</v>
       </c>
       <c r="G12">
-        <v>-18.43233411403749</v>
+        <v>-22.59735132026781</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.994864737589924</v>
       </c>
       <c r="E13">
-        <v>-35.47382132968938</v>
+        <v>-41.31978692278131</v>
       </c>
       <c r="F13">
-        <v>-6.563688816039105</v>
+        <v>-8.205515154869264</v>
       </c>
       <c r="G13">
-        <v>-17.27671536155302</v>
+        <v>-22.19959092899715</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.905890171447373</v>
       </c>
       <c r="E14">
-        <v>-35.49570518033144</v>
+        <v>-41.14181336580586</v>
       </c>
       <c r="F14">
-        <v>-6.576852975534716</v>
+        <v>-8.650023792317626</v>
       </c>
       <c r="G14">
-        <v>-16.73497106841561</v>
+        <v>-22.60402869062052</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.763812150678588</v>
       </c>
       <c r="E15">
-        <v>-36.20026780881484</v>
+        <v>-41.44918353907649</v>
       </c>
       <c r="F15">
-        <v>-6.560137355523731</v>
+        <v>-8.160162568568825</v>
       </c>
       <c r="G15">
-        <v>-17.12930173450759</v>
+        <v>-21.41016320552085</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.588256838681801</v>
       </c>
       <c r="E16">
-        <v>-36.18459249603729</v>
+        <v>-41.41168777429297</v>
       </c>
       <c r="F16">
-        <v>-7.054439290659424</v>
+        <v>-7.699112122833698</v>
       </c>
       <c r="G16">
-        <v>-16.75318900051822</v>
+        <v>-22.26120514730129</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.39931285793342</v>
       </c>
       <c r="E17">
-        <v>-36.68284237720523</v>
+        <v>-41.22407083191818</v>
       </c>
       <c r="F17">
-        <v>-6.527170141334986</v>
+        <v>-7.723443784592031</v>
       </c>
       <c r="G17">
-        <v>-16.6060633909347</v>
+        <v>-21.17790195157666</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.216393416295722</v>
       </c>
       <c r="E18">
-        <v>-36.55097321410187</v>
+        <v>-42.51823851196325</v>
       </c>
       <c r="F18">
-        <v>-6.428304924004806</v>
+        <v>-7.801200973554757</v>
       </c>
       <c r="G18">
-        <v>-16.70803812518087</v>
+        <v>-21.12797726957168</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.056604574283416</v>
       </c>
       <c r="E19">
-        <v>-38.28618256317597</v>
+        <v>-43.13470647133843</v>
       </c>
       <c r="F19">
-        <v>-5.961681813079727</v>
+        <v>-7.649744050184663</v>
       </c>
       <c r="G19">
-        <v>-16.34745516031622</v>
+        <v>-20.9007199052101</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.930734546379453</v>
       </c>
       <c r="E20">
-        <v>-38.17057288599715</v>
+        <v>-42.4820129841389</v>
       </c>
       <c r="F20">
-        <v>-6.014836526572578</v>
+        <v>-7.04741238751262</v>
       </c>
       <c r="G20">
-        <v>-15.62590024148606</v>
+        <v>-20.58204844687263</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.844648844395332</v>
       </c>
       <c r="E21">
-        <v>-38.78543550133661</v>
+        <v>-42.51672373740769</v>
       </c>
       <c r="F21">
-        <v>-6.127250348009344</v>
+        <v>-7.175270904963229</v>
       </c>
       <c r="G21">
-        <v>-16.35607747617325</v>
+        <v>-20.95658867173085</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.801079348968643</v>
       </c>
       <c r="E22">
-        <v>-38.47945104111233</v>
+        <v>-42.43715165638191</v>
       </c>
       <c r="F22">
-        <v>-5.793425729211609</v>
+        <v>-7.354423677382528</v>
       </c>
       <c r="G22">
-        <v>-15.37512807215904</v>
+        <v>-20.46380072602817</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.795640883269408</v>
       </c>
       <c r="E23">
-        <v>-38.94459324881019</v>
+        <v>-44.53618087146926</v>
       </c>
       <c r="F23">
-        <v>-5.782072933356782</v>
+        <v>-7.180945719184727</v>
       </c>
       <c r="G23">
-        <v>-16.16543805602155</v>
+        <v>-20.35456431014161</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.821729917634163</v>
       </c>
       <c r="E24">
-        <v>-39.99035375140151</v>
+        <v>-46.0249257584389</v>
       </c>
       <c r="F24">
-        <v>-5.254899202313749</v>
+        <v>-7.290892522731717</v>
       </c>
       <c r="G24">
-        <v>-15.38649317499535</v>
+        <v>-20.13329903320611</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.869755529761019</v>
       </c>
       <c r="E25">
-        <v>-40.756376829117</v>
+        <v>-43.84597350559018</v>
       </c>
       <c r="F25">
-        <v>-5.217777135655848</v>
+        <v>-7.572186408167283</v>
       </c>
       <c r="G25">
-        <v>-15.94790541918158</v>
+        <v>-20.71663205468062</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.927975060739884</v>
       </c>
       <c r="E26">
-        <v>-39.57594403801158</v>
+        <v>-43.68345563040291</v>
       </c>
       <c r="F26">
-        <v>-5.238599701032046</v>
+        <v>-7.146525058892087</v>
       </c>
       <c r="G26">
-        <v>-15.80064573250372</v>
+        <v>-19.66326115644931</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.985973432377266</v>
       </c>
       <c r="E27">
-        <v>-39.51045551114965</v>
+        <v>-43.78646256441838</v>
       </c>
       <c r="F27">
-        <v>-5.339865024677075</v>
+        <v>-6.824080950802701</v>
       </c>
       <c r="G27">
-        <v>-15.79205652210208</v>
+        <v>-20.43946325049622</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.031175031343133</v>
       </c>
       <c r="E28">
-        <v>-39.35841652481613</v>
+        <v>-45.81069950279505</v>
       </c>
       <c r="F28">
-        <v>-5.224646460064067</v>
+        <v>-7.444641068561451</v>
       </c>
       <c r="G28">
-        <v>-15.81263652844696</v>
+        <v>-19.91496358907287</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.050602227145663</v>
       </c>
       <c r="E29">
-        <v>-40.2425603185477</v>
+        <v>-44.20295311161483</v>
       </c>
       <c r="F29">
-        <v>-5.371152718742496</v>
+        <v>-6.814908917993433</v>
       </c>
       <c r="G29">
-        <v>-16.27433514099034</v>
+        <v>-20.0818713635263</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.035474967268931</v>
       </c>
       <c r="E30">
-        <v>-39.63749052824983</v>
+        <v>-44.09490825026583</v>
       </c>
       <c r="F30">
-        <v>-5.230228231563033</v>
+        <v>-7.500105617131972</v>
       </c>
       <c r="G30">
-        <v>-15.45519527129908</v>
+        <v>-21.23362174354813</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.976434203839922</v>
       </c>
       <c r="E31">
-        <v>-39.41507226312609</v>
+        <v>-44.76818591606723</v>
       </c>
       <c r="F31">
-        <v>-5.489941748341863</v>
+        <v>-7.137666995780556</v>
       </c>
       <c r="G31">
-        <v>-16.65331811796225</v>
+        <v>-20.51018312430613</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.867535559300909</v>
       </c>
       <c r="E32">
-        <v>-39.17696962827679</v>
+        <v>-43.89119484703077</v>
       </c>
       <c r="F32">
-        <v>-5.397412146526398</v>
+        <v>-7.053283185341154</v>
       </c>
       <c r="G32">
-        <v>-16.33666278185819</v>
+        <v>-20.59068731545736</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.707338644919121</v>
       </c>
       <c r="E33">
-        <v>-39.12955424117948</v>
+        <v>-45.17809432629353</v>
       </c>
       <c r="F33">
-        <v>-5.591827884705745</v>
+        <v>-7.667422959318713</v>
       </c>
       <c r="G33">
-        <v>-16.50828477315955</v>
+        <v>-20.5537681116034</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.493358762201091</v>
       </c>
       <c r="E34">
-        <v>-38.59629019898424</v>
+        <v>-43.43053809283752</v>
       </c>
       <c r="F34">
-        <v>-5.217034377581506</v>
+        <v>-7.178589956635511</v>
       </c>
       <c r="G34">
-        <v>-15.81500356850754</v>
+        <v>-20.52980803826293</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.229305796390564</v>
       </c>
       <c r="E35">
-        <v>-38.22566630077447</v>
+        <v>-43.0804893162816</v>
       </c>
       <c r="F35">
-        <v>-5.564725925374829</v>
+        <v>-6.972236243265582</v>
       </c>
       <c r="G35">
-        <v>-16.73817236595209</v>
+        <v>-21.01363433719079</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.9205218455876968</v>
       </c>
       <c r="E36">
-        <v>-37.84385933600277</v>
+        <v>-43.15273206212596</v>
       </c>
       <c r="F36">
-        <v>-5.338822154331758</v>
+        <v>-7.106135015077678</v>
       </c>
       <c r="G36">
-        <v>-16.49636846449095</v>
+        <v>-20.41165466796634</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.5705251271016629</v>
       </c>
       <c r="E37">
-        <v>-38.64858501682481</v>
+        <v>-44.11506448807397</v>
       </c>
       <c r="F37">
-        <v>-5.455066960377971</v>
+        <v>-6.86392976312051</v>
       </c>
       <c r="G37">
-        <v>-16.71367929477979</v>
+        <v>-20.74335643354639</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1903476895777754</v>
       </c>
       <c r="E38">
-        <v>-37.9760070002576</v>
+        <v>-42.91020057969716</v>
       </c>
       <c r="F38">
-        <v>-5.355684663066399</v>
+        <v>-6.881580165548081</v>
       </c>
       <c r="G38">
-        <v>-15.9495342075869</v>
+        <v>-20.79863757823391</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.2139840964679987</v>
       </c>
       <c r="E39">
-        <v>-37.10456331188054</v>
+        <v>-42.62865629369228</v>
       </c>
       <c r="F39">
-        <v>-5.385193855388783</v>
+        <v>-7.271085112847316</v>
       </c>
       <c r="G39">
-        <v>-16.72451967614813</v>
+        <v>-20.2147864563825</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.6351298300537913</v>
       </c>
       <c r="E40">
-        <v>-37.61227996796151</v>
+        <v>-42.87352673294605</v>
       </c>
       <c r="F40">
-        <v>-5.154431274597143</v>
+        <v>-6.909165155183207</v>
       </c>
       <c r="G40">
-        <v>-16.25088323639014</v>
+        <v>-19.80404045023405</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.061417454029685</v>
       </c>
       <c r="E41">
-        <v>-36.64017056663095</v>
+        <v>-42.89734197775238</v>
       </c>
       <c r="F41">
-        <v>-5.445900470539407</v>
+        <v>-6.815145682027792</v>
       </c>
       <c r="G41">
-        <v>-16.88514900098634</v>
+        <v>-20.73562630971219</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.489703235055098</v>
       </c>
       <c r="E42">
-        <v>-35.59201902976358</v>
+        <v>-41.8366035473807</v>
       </c>
       <c r="F42">
-        <v>-5.368637001895821</v>
+        <v>-6.690664417441856</v>
       </c>
       <c r="G42">
-        <v>-16.93294500220956</v>
+        <v>-20.69562333268841</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.910938365783542</v>
       </c>
       <c r="E43">
-        <v>-36.12836243428404</v>
+        <v>-42.1433125634462</v>
       </c>
       <c r="F43">
-        <v>-5.05240656396566</v>
+        <v>-6.582749508584376</v>
       </c>
       <c r="G43">
-        <v>-16.2835119732252</v>
+        <v>-20.00669052960222</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.31788103044637</v>
       </c>
       <c r="E44">
-        <v>-35.58281490634299</v>
+        <v>-41.34480221319969</v>
       </c>
       <c r="F44">
-        <v>-4.993468156469624</v>
+        <v>-6.95045989100181</v>
       </c>
       <c r="G44">
-        <v>-16.72796595405451</v>
+        <v>-20.60107580735959</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>2.707920156882624</v>
       </c>
       <c r="E45">
-        <v>-35.00838477118102</v>
+        <v>-40.83393600344638</v>
       </c>
       <c r="F45">
-        <v>-5.21691164037306</v>
+        <v>-7.057310549484116</v>
       </c>
       <c r="G45">
-        <v>-16.88470869842961</v>
+        <v>-20.85283451925731</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.071045625743992</v>
       </c>
       <c r="E46">
-        <v>-35.30717348620711</v>
+        <v>-41.22748303708297</v>
       </c>
       <c r="F46">
-        <v>-4.950327215480096</v>
+        <v>-6.919852002700591</v>
       </c>
       <c r="G46">
-        <v>-16.52037488546897</v>
+        <v>-20.53576536496085</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.404651723531138</v>
       </c>
       <c r="E47">
-        <v>-34.84650993930283</v>
+        <v>-41.24211453660175</v>
       </c>
       <c r="F47">
-        <v>-5.007608274735625</v>
+        <v>-6.781588537385545</v>
       </c>
       <c r="G47">
-        <v>-17.22529596823706</v>
+        <v>-20.96551721305026</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.706173141902325</v>
       </c>
       <c r="E48">
-        <v>-35.06036938855207</v>
+        <v>-41.90267398315261</v>
       </c>
       <c r="F48">
-        <v>-5.099170232236757</v>
+        <v>-6.606961600546093</v>
       </c>
       <c r="G48">
-        <v>-16.77537958726795</v>
+        <v>-20.38851892046515</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.970372126570281</v>
       </c>
       <c r="E49">
-        <v>-33.67816138108688</v>
+        <v>-40.18050437498358</v>
       </c>
       <c r="F49">
-        <v>-4.862914567477415</v>
+        <v>-6.888183427362507</v>
       </c>
       <c r="G49">
-        <v>-17.06510860122835</v>
+        <v>-20.04932207978419</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.201081759762149</v>
       </c>
       <c r="E50">
-        <v>-33.76646209576244</v>
+        <v>-40.56812590038114</v>
       </c>
       <c r="F50">
-        <v>-4.92149268187769</v>
+        <v>-6.51488256306357</v>
       </c>
       <c r="G50">
-        <v>-17.38233004061962</v>
+        <v>-21.05650259137882</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.399235337538271</v>
       </c>
       <c r="E51">
-        <v>-33.4953310357382</v>
+        <v>-40.35833981350181</v>
       </c>
       <c r="F51">
-        <v>-4.935861645648472</v>
+        <v>-6.142663765831358</v>
       </c>
       <c r="G51">
-        <v>-17.18154876420837</v>
+        <v>-19.90321446295399</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.566941140742422</v>
       </c>
       <c r="E52">
-        <v>-33.0070256834911</v>
+        <v>-40.45766736238605</v>
       </c>
       <c r="F52">
-        <v>-5.057185396565499</v>
+        <v>-6.938524687296581</v>
       </c>
       <c r="G52">
-        <v>-17.46605042676225</v>
+        <v>-20.06478729327089</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.710584392879475</v>
       </c>
       <c r="E53">
-        <v>-32.6445847378132</v>
+        <v>-39.74572105703315</v>
       </c>
       <c r="F53">
-        <v>-5.086913932157171</v>
+        <v>-7.045187280701427</v>
       </c>
       <c r="G53">
-        <v>-17.23742911763849</v>
+        <v>-21.53163705299333</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.831450750161193</v>
       </c>
       <c r="E54">
-        <v>-32.60135139646197</v>
+        <v>-37.8921781536646</v>
       </c>
       <c r="F54">
-        <v>-5.187080163896885</v>
+        <v>-6.270104580846771</v>
       </c>
       <c r="G54">
-        <v>-17.55071597365634</v>
+        <v>-20.40695369330058</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>4.935018530858935</v>
       </c>
       <c r="E55">
-        <v>-32.63366885121771</v>
+        <v>-38.81926773064792</v>
       </c>
       <c r="F55">
-        <v>-5.294693772703953</v>
+        <v>-6.854628262352654</v>
       </c>
       <c r="G55">
-        <v>-16.86054833708401</v>
+        <v>-20.33142690736764</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.027672231403701</v>
       </c>
       <c r="E56">
-        <v>-31.97607781937888</v>
+        <v>-39.02649975818693</v>
       </c>
       <c r="F56">
-        <v>-5.211527040260566</v>
+        <v>-6.583768623340961</v>
       </c>
       <c r="G56">
-        <v>-17.27043856721057</v>
+        <v>-20.17968970784792</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>5.111220485627448</v>
       </c>
       <c r="E57">
-        <v>-32.38699155083489</v>
+        <v>-39.45006604602037</v>
       </c>
       <c r="F57">
-        <v>-5.293030881492742</v>
+        <v>-6.788779354094598</v>
       </c>
       <c r="G57">
-        <v>-17.33535505469013</v>
+        <v>-21.43764900986065</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>5.192759006390796</v>
       </c>
       <c r="E58">
-        <v>-31.02033658734904</v>
+        <v>-38.54766344508987</v>
       </c>
       <c r="F58">
-        <v>-5.012765613049254</v>
+        <v>-6.76915842558174</v>
       </c>
       <c r="G58">
-        <v>-17.56038442190378</v>
+        <v>-20.17383997388002</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>5.277664586325997</v>
       </c>
       <c r="E59">
-        <v>-31.55005709863328</v>
+        <v>-37.86120112721514</v>
       </c>
       <c r="F59">
-        <v>-5.210342428235817</v>
+        <v>-6.926652435901489</v>
       </c>
       <c r="G59">
-        <v>-17.09613668929517</v>
+        <v>-21.18087813201647</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>5.367585149282402</v>
       </c>
       <c r="E60">
-        <v>-30.9769221070375</v>
+        <v>-36.79676746205319</v>
       </c>
       <c r="F60">
-        <v>-5.270514542639981</v>
+        <v>-7.321828238157432</v>
       </c>
       <c r="G60">
-        <v>-17.08237971730673</v>
+        <v>-21.44882375632846</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>5.467113179950791</v>
       </c>
       <c r="E61">
-        <v>-30.25746306330588</v>
+        <v>-38.45161903986119</v>
       </c>
       <c r="F61">
-        <v>-5.35801112705618</v>
+        <v>-7.000178358584638</v>
       </c>
       <c r="G61">
-        <v>-17.47755953832953</v>
+        <v>-20.4233226857195</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>5.575776176415498</v>
       </c>
       <c r="E62">
-        <v>-30.63126142179502</v>
+        <v>-37.65578728199021</v>
       </c>
       <c r="F62">
-        <v>-5.018352135665967</v>
+        <v>-6.737631195996608</v>
       </c>
       <c r="G62">
-        <v>-17.26321164629834</v>
+        <v>-21.62625906559678</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>5.69523038631465</v>
       </c>
       <c r="E63">
-        <v>-29.81761917565187</v>
+        <v>-36.71576438324099</v>
       </c>
       <c r="F63">
-        <v>-4.887706691730663</v>
+        <v>-7.269195751690196</v>
       </c>
       <c r="G63">
-        <v>-17.69861956144159</v>
+        <v>-21.87313306755131</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>5.827876719854061</v>
       </c>
       <c r="E64">
-        <v>-30.08645429935422</v>
+        <v>-37.92304649673789</v>
       </c>
       <c r="F64">
-        <v>-5.554176068419129</v>
+        <v>-7.2665343338993</v>
       </c>
       <c r="G64">
-        <v>-17.87453201976184</v>
+        <v>-21.52752204488801</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>5.969615547786743</v>
       </c>
       <c r="E65">
-        <v>-31.05876748201513</v>
+        <v>-38.28211146504308</v>
       </c>
       <c r="F65">
-        <v>-5.258661295715875</v>
+        <v>-7.005647291037129</v>
       </c>
       <c r="G65">
-        <v>-17.75948228590832</v>
+        <v>-21.49606524117386</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>6.120402124805312</v>
       </c>
       <c r="E66">
-        <v>-29.52945199641077</v>
+        <v>-38.85551363660531</v>
       </c>
       <c r="F66">
-        <v>-5.242839281767677</v>
+        <v>-7.068699770574999</v>
       </c>
       <c r="G66">
-        <v>-17.74146298653807</v>
+        <v>-21.39923509469572</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>6.279135514581673</v>
       </c>
       <c r="E67">
-        <v>-29.85730219338108</v>
+        <v>-37.89525072327881</v>
       </c>
       <c r="F67">
-        <v>-5.473745187944664</v>
+        <v>-7.392938613393057</v>
       </c>
       <c r="G67">
-        <v>-17.80038904186433</v>
+        <v>-21.08356133534405</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>6.440516038782614</v>
       </c>
       <c r="E68">
-        <v>-31.2019759440337</v>
+        <v>-38.17271258996578</v>
       </c>
       <c r="F68">
-        <v>-5.228604932999708</v>
+        <v>-6.994248963637233</v>
       </c>
       <c r="G68">
-        <v>-16.95633400644451</v>
+        <v>-20.76071527908156</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.60339187651993</v>
       </c>
       <c r="E69">
-        <v>-30.45721858025822</v>
+        <v>-37.44215199220435</v>
       </c>
       <c r="F69">
-        <v>-5.407946166422944</v>
+        <v>-7.332176172608913</v>
       </c>
       <c r="G69">
-        <v>-17.48938149645027</v>
+        <v>-22.09633335835451</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>6.761351742797288</v>
       </c>
       <c r="E70">
-        <v>-30.24317572781168</v>
+        <v>-37.59014025853801</v>
       </c>
       <c r="F70">
-        <v>-5.561693920399721</v>
+        <v>-7.280195381125881</v>
       </c>
       <c r="G70">
-        <v>-17.66028178882406</v>
+        <v>-21.4469135715523</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>6.910811590013908</v>
       </c>
       <c r="E71">
-        <v>-30.12367382722326</v>
+        <v>-36.81438322594303</v>
       </c>
       <c r="F71">
-        <v>-5.368052614413024</v>
+        <v>-8.110273852600088</v>
       </c>
       <c r="G71">
-        <v>-17.80649865365705</v>
+        <v>-21.06298960536302</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>7.049390768526296</v>
       </c>
       <c r="E72">
-        <v>-30.57454454908595</v>
+        <v>-37.97201288618283</v>
       </c>
       <c r="F72">
-        <v>-5.624011164466348</v>
+        <v>-7.2839950875435</v>
       </c>
       <c r="G72">
-        <v>-17.32591172353936</v>
+        <v>-21.06322630936908</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>7.168983060969134</v>
       </c>
       <c r="E73">
-        <v>-29.7482701246984</v>
+        <v>-36.67516434952522</v>
       </c>
       <c r="F73">
-        <v>-5.741416826948577</v>
+        <v>-7.23404143963223</v>
       </c>
       <c r="G73">
-        <v>-17.52135805581409</v>
+        <v>-21.19040091626018</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>7.265325448507919</v>
       </c>
       <c r="E74">
-        <v>-30.62452984518262</v>
+        <v>-36.16840320145987</v>
       </c>
       <c r="F74">
-        <v>-5.799727295049142</v>
+        <v>-7.557356981901587</v>
       </c>
       <c r="G74">
-        <v>-16.92126374227425</v>
+        <v>-20.51641853682935</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>7.3360431528798</v>
       </c>
       <c r="E75">
-        <v>-30.68527479552151</v>
+        <v>-36.85641199320822</v>
       </c>
       <c r="F75">
-        <v>-5.728914260599141</v>
+        <v>-7.69387837070965</v>
       </c>
       <c r="G75">
-        <v>-16.99348494848622</v>
+        <v>-21.5579194740296</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>7.376175974777052</v>
       </c>
       <c r="E76">
-        <v>-31.51670262332978</v>
+        <v>-39.21572657307144</v>
       </c>
       <c r="F76">
-        <v>-5.896108469650956</v>
+        <v>-7.466754354258732</v>
       </c>
       <c r="G76">
-        <v>-17.0522239579895</v>
+        <v>-21.06623393999151</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>7.386385756480191</v>
       </c>
       <c r="E77">
-        <v>-30.579885884178</v>
+        <v>-38.16778334600843</v>
       </c>
       <c r="F77">
-        <v>-5.868325516776403</v>
+        <v>-7.36768167145363</v>
       </c>
       <c r="G77">
-        <v>-16.98777260215821</v>
+        <v>-21.84529137956604</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>7.365930789891911</v>
       </c>
       <c r="E78">
-        <v>-31.19791390284882</v>
+        <v>-37.18608037249261</v>
       </c>
       <c r="F78">
-        <v>-5.996452868306157</v>
+        <v>-7.511884429878052</v>
       </c>
       <c r="G78">
-        <v>-16.71937177783456</v>
+        <v>-19.96477902307505</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>7.314869567212292</v>
       </c>
       <c r="E79">
-        <v>-32.02892511104839</v>
+        <v>-37.90886784461988</v>
       </c>
       <c r="F79">
-        <v>-5.829537391495459</v>
+        <v>-7.392327302909698</v>
       </c>
       <c r="G79">
-        <v>-16.98996252803243</v>
+        <v>-20.84612569872198</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>7.235822938292658</v>
       </c>
       <c r="E80">
-        <v>-32.36979467079076</v>
+        <v>-40.05508375886715</v>
       </c>
       <c r="F80">
-        <v>-6.418800312953295</v>
+        <v>-7.475653593724066</v>
       </c>
       <c r="G80">
-        <v>-15.85096767997341</v>
+        <v>-20.16487998237799</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>7.12686179554245</v>
       </c>
       <c r="E81">
-        <v>-32.61455189819433</v>
+        <v>-38.89845262714604</v>
       </c>
       <c r="F81">
-        <v>-6.147857133454563</v>
+        <v>-7.748487322159354</v>
       </c>
       <c r="G81">
-        <v>-15.94190836593719</v>
+        <v>-20.84798291476951</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>6.984529688212138</v>
       </c>
       <c r="E82">
-        <v>-32.12435364381203</v>
+        <v>-40.0247067552237</v>
       </c>
       <c r="F82">
-        <v>-6.13410304350545</v>
+        <v>-7.825438008884642</v>
       </c>
       <c r="G82">
-        <v>-16.81117651618409</v>
+        <v>-20.91321721462085</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>6.810481956070523</v>
       </c>
       <c r="E83">
-        <v>-32.74155295173944</v>
+        <v>-41.0562319997719</v>
       </c>
       <c r="F83">
-        <v>-6.320825138347592</v>
+        <v>-7.539644023090355</v>
       </c>
       <c r="G83">
-        <v>-16.20098338347671</v>
+        <v>-19.98212462642806</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>6.599171049226547</v>
       </c>
       <c r="E84">
-        <v>-34.47143002266952</v>
+        <v>-41.16557879739811</v>
       </c>
       <c r="F84">
-        <v>-6.257525204760435</v>
+        <v>-7.714709646468383</v>
       </c>
       <c r="G84">
-        <v>-16.27439473081004</v>
+        <v>-20.66409038642685</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.346376843524583</v>
       </c>
       <c r="E85">
-        <v>-34.65847184884533</v>
+        <v>-41.53799597131491</v>
       </c>
       <c r="F85">
-        <v>-5.850212672221521</v>
+        <v>-7.572889969520217</v>
       </c>
       <c r="G85">
-        <v>-16.56363709457617</v>
+        <v>-20.5597486121201</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.051104346540622</v>
       </c>
       <c r="E86">
-        <v>-35.20878785991646</v>
+        <v>-42.07238986777507</v>
       </c>
       <c r="F86">
-        <v>-6.050285407930818</v>
+        <v>-7.443450121713041</v>
       </c>
       <c r="G86">
-        <v>-17.0202192589886</v>
+        <v>-19.78734702435227</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.706264164286268</v>
       </c>
       <c r="E87">
-        <v>-35.33425828924698</v>
+        <v>-42.24561758399049</v>
       </c>
       <c r="F87">
-        <v>-6.377168643701181</v>
+        <v>-7.653440815717777</v>
       </c>
       <c r="G87">
-        <v>-16.32253006295105</v>
+        <v>-20.5239930650232</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.312180133138154</v>
       </c>
       <c r="E88">
-        <v>-36.64334955538433</v>
+        <v>-43.18543443717235</v>
       </c>
       <c r="F88">
-        <v>-6.189098023272043</v>
+        <v>-8.045239365109046</v>
       </c>
       <c r="G88">
-        <v>-16.27368461879187</v>
+        <v>-21.8197372785484</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.869399326146403</v>
       </c>
       <c r="E89">
-        <v>-37.75976783791733</v>
+        <v>-42.15330011287012</v>
       </c>
       <c r="F89">
-        <v>-6.357005295912285</v>
+        <v>-7.352037824420918</v>
       </c>
       <c r="G89">
-        <v>-15.80450913914805</v>
+        <v>-20.35219230426272</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.372044701597588</v>
       </c>
       <c r="E90">
-        <v>-38.5857569684424</v>
+        <v>-43.87067406706502</v>
       </c>
       <c r="F90">
-        <v>-6.519366034510179</v>
+        <v>-8.052761968207383</v>
       </c>
       <c r="G90">
-        <v>-15.95312946004255</v>
+        <v>-20.48771279645833</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.827862319086198</v>
       </c>
       <c r="E91">
-        <v>-39.87380215162909</v>
+        <v>-45.78704728305298</v>
       </c>
       <c r="F91">
-        <v>-6.563841643659944</v>
+        <v>-8.053127804273849</v>
       </c>
       <c r="G91">
-        <v>-15.27136067750335</v>
+        <v>-20.52819911313084</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.235712288454526</v>
       </c>
       <c r="E92">
-        <v>-41.09260696723851</v>
+        <v>-45.76575892674293</v>
       </c>
       <c r="F92">
-        <v>-6.228092030321993</v>
+        <v>-7.422412172332344</v>
       </c>
       <c r="G92">
-        <v>-16.08738366856938</v>
+        <v>-20.90008262519379</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.594782724974436</v>
       </c>
       <c r="E93">
-        <v>-41.4531504823072</v>
+        <v>-47.2143181353685</v>
       </c>
       <c r="F93">
-        <v>-6.375083298937026</v>
+        <v>-7.64140742224579</v>
       </c>
       <c r="G93">
-        <v>-15.85629103720056</v>
+        <v>-20.04187169704806</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.915610103352659</v>
       </c>
       <c r="E94">
-        <v>-42.5683324914361</v>
+        <v>-48.35848917085751</v>
       </c>
       <c r="F94">
-        <v>-6.742478523877289</v>
+        <v>-7.499255167055381</v>
       </c>
       <c r="G94">
-        <v>-16.35471518668384</v>
+        <v>-21.19997997977806</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.198071312328268</v>
       </c>
       <c r="E95">
-        <v>-44.11843367273568</v>
+        <v>-47.7497354669544</v>
       </c>
       <c r="F95">
-        <v>-6.494980526750722</v>
+        <v>-8.064110408870944</v>
       </c>
       <c r="G95">
-        <v>-16.76767098197976</v>
+        <v>-21.03862730073952</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.4453471650274349</v>
       </c>
       <c r="E96">
-        <v>-45.88423059949459</v>
+        <v>-50.97185114255104</v>
       </c>
       <c r="F96">
-        <v>-6.593996196142869</v>
+        <v>-7.810899588580908</v>
       </c>
       <c r="G96">
-        <v>-17.30532509610341</v>
+        <v>-20.83704156176222</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3242175782232064</v>
       </c>
       <c r="E97">
-        <v>-46.96964468473408</v>
+        <v>-51.80511187021392</v>
       </c>
       <c r="F97">
-        <v>-6.780930903504158</v>
+        <v>-7.83761353996254</v>
       </c>
       <c r="G97">
-        <v>-17.49609528280391</v>
+        <v>-21.124547544393</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.12812164096241</v>
       </c>
       <c r="E98">
-        <v>-49.08325445400762</v>
+        <v>-52.86757225282702</v>
       </c>
       <c r="F98">
-        <v>-6.689133765674584</v>
+        <v>-7.775756758390827</v>
       </c>
       <c r="G98">
-        <v>-17.45595657341302</v>
+        <v>-21.04886019700141</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.92727816896668</v>
       </c>
       <c r="E99">
-        <v>-49.58474332620955</v>
+        <v>-53.48252543764664</v>
       </c>
       <c r="F99">
-        <v>-6.967261822985187</v>
+        <v>-7.644906224539474</v>
       </c>
       <c r="G99">
-        <v>-17.22171395796357</v>
+        <v>-22.38361256861585</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.759051862689166</v>
       </c>
       <c r="E100">
-        <v>-51.87416770247539</v>
+        <v>-54.84341565372072</v>
       </c>
       <c r="F100">
-        <v>-6.851408192300087</v>
+        <v>-7.59461010022399</v>
       </c>
       <c r="G100">
-        <v>-17.13361206479972</v>
+        <v>-20.87927088066117</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.553920698148644</v>
       </c>
       <c r="E101">
-        <v>-52.95181545479171</v>
+        <v>-55.50891566541394</v>
       </c>
       <c r="F101">
-        <v>-6.784460192136716</v>
+        <v>-7.260700753159779</v>
       </c>
       <c r="G101">
-        <v>-17.85147241480805</v>
+        <v>-21.85025057678386</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.410404455618402</v>
       </c>
       <c r="E102">
-        <v>-55.0500997359048</v>
+        <v>-57.94331064614659</v>
       </c>
       <c r="F102">
-        <v>-6.930219733476016</v>
+        <v>-7.572836519445571</v>
       </c>
       <c r="G102">
-        <v>-17.56499104602168</v>
+        <v>-21.69390013205517</v>
       </c>
     </row>
   </sheetData>
